--- a/sw/Languajes/Basic/Microsoft Basic/MS Basic Evolucion.xlsx
+++ b/sw/Languajes/Basic/Microsoft Basic/MS Basic Evolucion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="406">
   <si>
     <t>Brand Name</t>
   </si>
@@ -1335,6 +1335,25 @@
   </si>
   <si>
     <t>screen mode/graphic resolution; as function returns char at given row, col</t>
+  </si>
+  <si>
+    <t>Altair Basic 2.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEMORY SIZE?
+STRING SPACE?
+WANT SIN? Y
+61921 BYTES FREE
+ALTAIR BASIC VERSION 3.0
+[FOUR-K VERSION]
+OK
+</t>
+  </si>
+  <si>
+    <t>FREE</t>
   </si>
 </sst>
 </file>
@@ -1709,16 +1728,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:X202"/>
+  <dimension ref="A2:Y202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="22" width="9.1796875" style="1"/>
-    <col min="23" max="23" width="4.54296875" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.1796875" style="1"/>
+    <col min="2" max="23" width="9.1796875" style="1"/>
+    <col min="24" max="24" width="4.54296875" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1726,67 +1745,70 @@
         <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>193</v>
       </c>
@@ -1803,10 +1825,10 @@
         <v>1975</v>
       </c>
       <c r="F3" s="2">
+        <v>1975</v>
+      </c>
+      <c r="G3" s="2">
         <v>1976</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1977</v>
       </c>
       <c r="H3" s="2">
         <v>1977</v>
@@ -1815,10 +1837,10 @@
         <v>1977</v>
       </c>
       <c r="J3" s="2">
+        <v>1977</v>
+      </c>
+      <c r="K3" s="2">
         <v>1978</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1977</v>
       </c>
       <c r="L3" s="2">
         <v>1977</v>
@@ -1827,35 +1849,38 @@
         <v>1977</v>
       </c>
       <c r="N3" s="2">
+        <v>1977</v>
+      </c>
+      <c r="O3" s="2">
         <v>1978</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>1979</v>
-      </c>
-      <c r="P3" s="2">
-        <v>1980</v>
       </c>
       <c r="Q3" s="2">
         <v>1980</v>
       </c>
       <c r="R3" s="2">
+        <v>1980</v>
+      </c>
+      <c r="S3" s="2">
         <v>1981</v>
       </c>
-      <c r="S3" s="2">
+      <c r="T3" s="2">
         <v>1982</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>1985</v>
       </c>
-      <c r="U3" s="2">
+      <c r="V3" s="2">
         <v>1983</v>
       </c>
-      <c r="V3" s="2">
+      <c r="W3" s="2">
         <v>1988</v>
       </c>
-      <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1881,22 +1906,25 @@
         <v>6</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>188</v>
       </c>
@@ -1922,13 +1950,13 @@
         <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>195</v>
@@ -1937,10 +1965,10 @@
         <v>195</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>195</v>
@@ -1963,8 +1991,11 @@
       <c r="V5" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W5" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1975,26 +2006,24 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>230</v>
@@ -2011,14 +2040,17 @@
       <c r="T6" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="U6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -2026,67 +2058,70 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>1.3</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -2094,31 +2129,31 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>228</v>
@@ -2127,10 +2162,10 @@
         <v>228</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>86</v>
@@ -2148,10 +2183,13 @@
         <v>86</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>273</v>
       </c>
@@ -2161,15 +2199,15 @@
       </c>
       <c r="C9" s="2">
         <f>COUNTA(C12:C197)</f>
+        <v>60</v>
+      </c>
+      <c r="D9" s="2">
+        <f>COUNTA(D12:D197)</f>
         <v>32</v>
       </c>
-      <c r="D9" s="2">
-        <f t="shared" ref="D9:T9" si="0">COUNTA(D12:D197)</f>
+      <c r="E9" s="2">
+        <f t="shared" ref="E9:U9" si="0">COUNTA(E12:E197)</f>
         <v>32</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>62</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
@@ -2177,43 +2215,43 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="0"/>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="0"/>
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="O9" s="2">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="0"/>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q9" s="2">
         <f t="shared" si="0"/>
@@ -2225,22 +2263,26 @@
       </c>
       <c r="S9" s="2">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T9" s="2">
         <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+      <c r="U9" s="2">
+        <f t="shared" si="0"/>
         <v>131</v>
-      </c>
-      <c r="U9" s="2">
-        <f>COUNTA(U12:U294)</f>
-        <v>157</v>
       </c>
       <c r="V9" s="2">
         <f>COUNTA(V12:V294)</f>
+        <v>157</v>
+      </c>
+      <c r="W9" s="2">
+        <f>COUNTA(W12:W294)</f>
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="3" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" s="3" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -2248,67 +2290,70 @@
         <v>269</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="M10" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="N10" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="T10" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="W10" s="4" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>313</v>
       </c>
@@ -2316,70 +2361,73 @@
         <v>1521</v>
       </c>
       <c r="C11" s="7">
+        <v>59047</v>
+      </c>
+      <c r="D11" s="7">
         <v>61921</v>
       </c>
-      <c r="D11" s="7">
+      <c r="E11" s="7">
         <v>61911</v>
       </c>
-      <c r="E11" s="7">
+      <c r="F11" s="7">
         <v>59208</v>
       </c>
-      <c r="F11" s="7">
+      <c r="G11" s="7">
         <v>58756</v>
       </c>
-      <c r="G11" s="8">
+      <c r="H11" s="8">
         <v>50606</v>
       </c>
-      <c r="H11" s="8">
+      <c r="I11" s="8">
         <v>48178</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <v>30332</v>
       </c>
-      <c r="J11" s="8">
+      <c r="K11" s="8">
         <v>42880</v>
       </c>
-      <c r="K11" s="8">
+      <c r="L11" s="8">
         <v>39933</v>
       </c>
-      <c r="L11" s="8">
+      <c r="M11" s="8">
         <v>39847</v>
       </c>
-      <c r="M11" s="8">
+      <c r="N11" s="8">
         <v>39673</v>
       </c>
-      <c r="N11" s="8">
+      <c r="O11" s="8">
         <v>6586</v>
       </c>
-      <c r="O11" s="8">
+      <c r="P11" s="8">
         <v>33815</v>
       </c>
-      <c r="P11" s="8">
+      <c r="Q11" s="8">
         <v>33243</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="R11" s="8">
         <v>33094</v>
       </c>
-      <c r="R11" s="8">
+      <c r="S11" s="8">
         <v>33107</v>
       </c>
-      <c r="S11" s="8">
+      <c r="T11" s="8">
         <v>34063</v>
       </c>
-      <c r="T11" s="8">
+      <c r="U11" s="8">
         <v>33080</v>
       </c>
-      <c r="U11" s="7">
+      <c r="V11" s="7">
         <v>56235</v>
       </c>
-      <c r="V11" s="7">
+      <c r="W11" s="7">
         <v>60300</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
@@ -2443,9 +2491,12 @@
       <c r="V13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
@@ -2468,7 +2519,7 @@
         <v>48</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>152</v>
@@ -2483,7 +2534,7 @@
         <v>152</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>48</v>
@@ -2509,9 +2560,12 @@
       <c r="V14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>27</v>
       </c>
@@ -2528,7 +2582,7 @@
         <v>27</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>136</v>
@@ -2549,7 +2603,7 @@
         <v>136</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>27</v>
@@ -2575,12 +2629,12 @@
       <c r="V15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="G16" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="W15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
         <v>135</v>
       </c>
@@ -2599,7 +2653,7 @@
       <c r="M16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>135</v>
       </c>
       <c r="P16" s="1" t="s">
@@ -2623,12 +2677,12 @@
       <c r="V16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G17" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="W16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H17" s="1" t="s">
         <v>88</v>
       </c>
@@ -2647,7 +2701,7 @@
       <c r="M17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P17" s="1" t="s">
@@ -2671,12 +2725,12 @@
       <c r="V17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G18" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="W17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H18" s="1" t="s">
         <v>197</v>
       </c>
@@ -2695,8 +2749,8 @@
       <c r="M18" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>264</v>
+      <c r="N18" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>264</v>
@@ -2719,12 +2773,12 @@
       <c r="V18" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G19" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="W18" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H19" s="1" t="s">
         <v>102</v>
       </c>
@@ -2743,7 +2797,7 @@
       <c r="M19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P19" s="1" t="s">
@@ -2767,15 +2821,15 @@
       <c r="V19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W19" s="2"/>
-      <c r="X19" s="1" t="s">
+      <c r="W19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G20" s="1" t="s">
-        <v>106</v>
-      </c>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H20" s="1" t="s">
         <v>106</v>
       </c>
@@ -2794,7 +2848,7 @@
       <c r="M20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>106</v>
       </c>
       <c r="P20" s="1" t="s">
@@ -2818,12 +2872,12 @@
       <c r="V20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G21" s="1" t="s">
-        <v>179</v>
-      </c>
+      <c r="W20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H21" s="1" t="s">
         <v>179</v>
       </c>
@@ -2842,7 +2896,7 @@
       <c r="M21" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>179</v>
       </c>
       <c r="P21" s="1" t="s">
@@ -2866,12 +2920,12 @@
       <c r="V21" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G22" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="W21" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H22" s="1" t="s">
         <v>178</v>
       </c>
@@ -2890,7 +2944,7 @@
       <c r="M22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>178</v>
       </c>
       <c r="P22" s="1" t="s">
@@ -2914,13 +2968,13 @@
       <c r="V22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="I23" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K23" s="1" t="s">
+      <c r="W22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="J23" s="1" t="s">
         <v>200</v>
       </c>
       <c r="L23" s="1" t="s">
@@ -2930,10 +2984,10 @@
         <v>200</v>
       </c>
       <c r="N23" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>200</v>
@@ -2956,9 +3010,12 @@
       <c r="V23" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W23" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2975,7 +3032,7 @@
         <v>18</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>163</v>
@@ -2996,7 +3053,7 @@
         <v>163</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>18</v>
@@ -3022,9 +3079,12 @@
       <c r="V24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>9</v>
       </c>
@@ -3041,7 +3101,7 @@
         <v>9</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>103</v>
@@ -3062,7 +3122,7 @@
         <v>103</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>9</v>
@@ -3088,9 +3148,12 @@
       <c r="V25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
@@ -3107,7 +3170,7 @@
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>170</v>
@@ -3128,7 +3191,7 @@
         <v>170</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>25</v>
@@ -3154,10 +3217,13 @@
       <c r="V26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="E27" s="1" t="s">
+      <c r="W26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C27" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -3211,9 +3277,12 @@
       <c r="V27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3230,7 +3299,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>166</v>
@@ -3251,7 +3320,7 @@
         <v>166</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>24</v>
@@ -3277,9 +3346,12 @@
       <c r="V28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>21</v>
       </c>
@@ -3296,7 +3368,7 @@
         <v>21</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>120</v>
@@ -3317,7 +3389,7 @@
         <v>120</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>21</v>
@@ -3343,9 +3415,12 @@
       <c r="V29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>22</v>
       </c>
@@ -3362,7 +3437,7 @@
         <v>22</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>165</v>
@@ -3383,7 +3458,7 @@
         <v>165</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>22</v>
@@ -3409,9 +3484,12 @@
       <c r="V30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>23</v>
       </c>
@@ -3428,7 +3506,7 @@
         <v>23</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>154</v>
@@ -3449,7 +3527,7 @@
         <v>154</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>23</v>
@@ -3475,8 +3553,11 @@
       <c r="V31" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W31" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>17</v>
       </c>
@@ -3493,7 +3574,7 @@
         <v>17</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>118</v>
@@ -3514,7 +3595,7 @@
         <v>118</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>17</v>
@@ -3540,12 +3621,12 @@
       <c r="V32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G33" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="W32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H33" s="1" t="s">
         <v>119</v>
       </c>
@@ -3564,7 +3645,7 @@
       <c r="M33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>119</v>
       </c>
       <c r="P33" s="1" t="s">
@@ -3588,12 +3669,12 @@
       <c r="V33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G34" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="W33" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H34" s="1" t="s">
         <v>107</v>
       </c>
@@ -3612,7 +3693,7 @@
       <c r="M34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>107</v>
       </c>
       <c r="P34" s="1" t="s">
@@ -3636,15 +3717,15 @@
       <c r="V34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="W34" s="2"/>
-      <c r="X34" s="1" t="s">
+      <c r="W34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G35" s="1" t="s">
-        <v>108</v>
-      </c>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H35" s="1" t="s">
         <v>108</v>
       </c>
@@ -3663,7 +3744,7 @@
       <c r="M35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>108</v>
       </c>
       <c r="P35" s="1" t="s">
@@ -3687,12 +3768,12 @@
       <c r="V35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G36" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="W35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H36" s="1" t="s">
         <v>109</v>
       </c>
@@ -3711,7 +3792,7 @@
       <c r="M36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>109</v>
       </c>
       <c r="P36" s="1" t="s">
@@ -3735,12 +3816,12 @@
       <c r="V36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G37" s="1" t="s">
-        <v>167</v>
-      </c>
+      <c r="W36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H37" s="1" t="s">
         <v>167</v>
       </c>
@@ -3759,7 +3840,7 @@
       <c r="M37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O37" s="1" t="s">
+      <c r="N37" s="1" t="s">
         <v>167</v>
       </c>
       <c r="P37" s="1" t="s">
@@ -3783,12 +3864,15 @@
       <c r="V37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="W37" s="2"/>
-      <c r="X37" s="1" t="s">
+      <c r="W37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="1" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -3805,7 +3889,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>113</v>
@@ -3826,7 +3910,7 @@
         <v>113</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>10</v>
@@ -3852,9 +3936,12 @@
       <c r="V38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3918,9 +4005,12 @@
       <c r="V39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3984,9 +4074,12 @@
       <c r="V40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X40" s="2"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
@@ -4003,7 +4096,7 @@
         <v>11</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>149</v>
@@ -4024,7 +4117,7 @@
         <v>149</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>11</v>
@@ -4050,9 +4143,12 @@
       <c r="V41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="X41" s="2"/>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
@@ -4069,7 +4165,7 @@
         <v>19</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>124</v>
@@ -4090,7 +4186,7 @@
         <v>124</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>19</v>
@@ -4116,9 +4212,12 @@
       <c r="V42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X42" s="2"/>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>32</v>
       </c>
@@ -4182,11 +4281,11 @@
       <c r="V43" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G44" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="W43" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H44" s="1" t="s">
         <v>104</v>
       </c>
@@ -4205,7 +4304,7 @@
       <c r="M44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O44" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>104</v>
       </c>
       <c r="P44" s="1" t="s">
@@ -4229,12 +4328,12 @@
       <c r="V44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="W44" s="2"/>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="O45" s="1" t="s">
-        <v>267</v>
-      </c>
+      <c r="W44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="X44" s="2"/>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.3">
       <c r="P45" s="1" t="s">
         <v>267</v>
       </c>
@@ -4256,12 +4355,12 @@
       <c r="V45" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="W45" s="2"/>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="O46" s="1" t="s">
-        <v>266</v>
-      </c>
+      <c r="W45" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="X45" s="2"/>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.3">
       <c r="P46" s="1" t="s">
         <v>266</v>
       </c>
@@ -4283,9 +4382,12 @@
       <c r="V46" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="W46" s="2"/>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W46" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="X46" s="2"/>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>12</v>
       </c>
@@ -4302,7 +4404,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>96</v>
@@ -4323,7 +4425,7 @@
         <v>96</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>12</v>
@@ -4349,9 +4451,12 @@
       <c r="V47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W47" s="2"/>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="X47" s="2"/>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
@@ -4368,7 +4473,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>162</v>
@@ -4389,7 +4494,7 @@
         <v>162</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>15</v>
@@ -4415,9 +4520,12 @@
       <c r="V48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W48" s="2"/>
-    </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="X48" s="2"/>
+    </row>
+    <row r="49" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>20</v>
       </c>
@@ -4434,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>164</v>
@@ -4455,7 +4563,7 @@
         <v>164</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>20</v>
@@ -4481,9 +4589,12 @@
       <c r="V49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W49" s="2"/>
-    </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X49" s="2"/>
+    </row>
+    <row r="50" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>13</v>
       </c>
@@ -4500,7 +4611,7 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>123</v>
@@ -4521,7 +4632,7 @@
         <v>123</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>13</v>
@@ -4547,12 +4658,12 @@
       <c r="V50" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G51" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="W50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X50" s="2"/>
+    </row>
+    <row r="51" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H51" s="1" t="s">
         <v>359</v>
       </c>
@@ -4571,7 +4682,7 @@
       <c r="M51" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="O51" s="1" t="s">
+      <c r="N51" s="1" t="s">
         <v>359</v>
       </c>
       <c r="P51" s="1" t="s">
@@ -4595,12 +4706,12 @@
       <c r="V51" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="W51" s="2"/>
-    </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="P52" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="W51" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="X51" s="2"/>
+    </row>
+    <row r="52" spans="2:25" x14ac:dyDescent="0.3">
       <c r="Q52" s="1" t="s">
         <v>260</v>
       </c>
@@ -4619,9 +4730,12 @@
       <c r="V52" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="W52" s="2"/>
-    </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W52" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="X52" s="2"/>
+    </row>
+    <row r="53" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
@@ -4638,7 +4752,7 @@
         <v>26</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>159</v>
@@ -4659,7 +4773,7 @@
         <v>159</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>26</v>
@@ -4685,9 +4799,12 @@
       <c r="V53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W53" s="2"/>
-    </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="W53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X53" s="2"/>
+    </row>
+    <row r="54" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>30</v>
       </c>
@@ -4751,10 +4868,13 @@
       <c r="V54" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W54" s="2"/>
-    </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="E55" s="1" t="s">
+      <c r="W54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X54" s="2"/>
+    </row>
+    <row r="55" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C55" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -4808,17 +4928,20 @@
       <c r="V55" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="2"/>
-    </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="E56" s="1" t="s">
+      <c r="W55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X55" s="2"/>
+    </row>
+    <row r="56" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C56" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>66</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>160</v>
@@ -4839,7 +4962,7 @@
         <v>160</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>66</v>
@@ -4865,15 +4988,15 @@
       <c r="V56" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="W56" s="2"/>
-      <c r="X56" s="1" t="s">
+      <c r="W56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G57" s="1" t="s">
-        <v>181</v>
-      </c>
+    <row r="57" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H57" s="1" t="s">
         <v>181</v>
       </c>
@@ -4892,7 +5015,7 @@
       <c r="M57" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="O57" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>181</v>
       </c>
       <c r="P57" s="1" t="s">
@@ -4916,12 +5039,12 @@
       <c r="V57" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G58" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="W57" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="X57" s="2"/>
+    </row>
+    <row r="58" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H58" s="1" t="s">
         <v>134</v>
       </c>
@@ -4940,7 +5063,7 @@
       <c r="M58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="O58" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>134</v>
       </c>
       <c r="P58" s="1" t="s">
@@ -4964,12 +5087,12 @@
       <c r="V58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G59" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="W58" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="X58" s="2"/>
+    </row>
+    <row r="59" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H59" s="1" t="s">
         <v>137</v>
       </c>
@@ -4988,8 +5111,8 @@
       <c r="M59" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="O59" s="1" t="s">
-        <v>261</v>
+      <c r="N59" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>261</v>
@@ -5012,15 +5135,15 @@
       <c r="V59" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="W59" s="2"/>
-      <c r="X59" s="1" t="s">
+      <c r="W59" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="X59" s="2"/>
+      <c r="Y59" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G60" s="1" t="s">
-        <v>185</v>
-      </c>
+    <row r="60" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H60" s="1" t="s">
         <v>185</v>
       </c>
@@ -5066,15 +5189,15 @@
       <c r="V60" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="W60" s="2"/>
-      <c r="X60" s="1" t="s">
+      <c r="W60" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="O61" s="1" t="s">
-        <v>268</v>
-      </c>
+    <row r="61" spans="2:25" x14ac:dyDescent="0.3">
       <c r="P61" s="1" t="s">
         <v>268</v>
       </c>
@@ -5096,12 +5219,15 @@
       <c r="V61" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="W61" s="2"/>
-      <c r="X61" s="1" t="s">
+      <c r="W61" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>14</v>
       </c>
@@ -5118,7 +5244,7 @@
         <v>14</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>97</v>
@@ -5139,7 +5265,7 @@
         <v>97</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>14</v>
@@ -5165,12 +5291,12 @@
       <c r="V62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G63" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="W62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="X62" s="2"/>
+    </row>
+    <row r="63" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H63" s="1" t="s">
         <v>105</v>
       </c>
@@ -5189,7 +5315,7 @@
       <c r="M63" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="O63" s="1" t="s">
+      <c r="N63" s="1" t="s">
         <v>105</v>
       </c>
       <c r="P63" s="1" t="s">
@@ -5213,15 +5339,15 @@
       <c r="V63" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="W63" s="2"/>
-      <c r="X63" s="1" t="s">
+      <c r="W63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="G64" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="64" spans="2:25" x14ac:dyDescent="0.3">
       <c r="H64" s="1" t="s">
         <v>171</v>
       </c>
@@ -5240,7 +5366,7 @@
       <c r="M64" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O64" s="1" t="s">
+      <c r="N64" s="1" t="s">
         <v>171</v>
       </c>
       <c r="P64" s="1" t="s">
@@ -5264,12 +5390,12 @@
       <c r="V64" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W64" s="2"/>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="G65" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="W64" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="X64" s="2"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
       <c r="H65" s="1" t="s">
         <v>184</v>
       </c>
@@ -5288,7 +5414,7 @@
       <c r="M65" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="O65" s="1" t="s">
+      <c r="N65" s="1" t="s">
         <v>184</v>
       </c>
       <c r="P65" s="1" t="s">
@@ -5312,12 +5438,12 @@
       <c r="V65" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="W65" s="2"/>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="N66" s="1" t="s">
-        <v>263</v>
-      </c>
+      <c r="W65" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="X65" s="2"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
       <c r="O66" s="1" t="s">
         <v>263</v>
       </c>
@@ -5342,9 +5468,12 @@
       <c r="V66" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="W66" s="2"/>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W66" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="X66" s="2"/>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>16</v>
       </c>
@@ -5361,7 +5490,7 @@
         <v>16</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>130</v>
@@ -5382,7 +5511,7 @@
         <v>130</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>16</v>
@@ -5408,9 +5537,12 @@
       <c r="V67" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="W67" s="2"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X67" s="2"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>35</v>
       </c>
@@ -5427,7 +5559,7 @@
         <v>35</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>126</v>
@@ -5448,7 +5580,7 @@
         <v>126</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>35</v>
@@ -5474,9 +5606,12 @@
       <c r="V68" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="W68" s="2"/>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X68" s="2"/>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>39</v>
       </c>
@@ -5493,7 +5628,7 @@
         <v>39</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>169</v>
@@ -5514,7 +5649,7 @@
         <v>169</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>39</v>
@@ -5540,9 +5675,12 @@
       <c r="V69" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W69" s="2"/>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W69" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="X69" s="2"/>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>36</v>
       </c>
@@ -5606,9 +5744,12 @@
       <c r="V70" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W70" s="2"/>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X70" s="2"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
         <v>34</v>
       </c>
@@ -5625,7 +5766,7 @@
         <v>34</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>173</v>
@@ -5646,7 +5787,7 @@
         <v>173</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>34</v>
@@ -5672,9 +5813,12 @@
       <c r="V71" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="W71" s="2"/>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X71" s="2"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
         <v>42</v>
       </c>
@@ -5691,7 +5835,7 @@
         <v>42</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>175</v>
@@ -5712,7 +5856,7 @@
         <v>175</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>42</v>
@@ -5738,13 +5882,16 @@
       <c r="V72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W72" s="2"/>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X72" s="2"/>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -5798,13 +5945,16 @@
       <c r="V73" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="W73" s="2"/>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W73" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73" s="2"/>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -5858,20 +6008,23 @@
       <c r="V74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W74" s="2"/>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X74" s="2"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>110</v>
@@ -5892,7 +6045,7 @@
         <v>110</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="O75" s="1" t="s">
         <v>38</v>
@@ -5918,20 +6071,23 @@
       <c r="V75" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="W75" s="2"/>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="X75" s="2"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>138</v>
@@ -5952,7 +6108,7 @@
         <v>138</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="O76" s="1" t="s">
         <v>37</v>
@@ -5978,9 +6134,12 @@
       <c r="V76" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="W76" s="2"/>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W76" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X76" s="2"/>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>40</v>
       </c>
@@ -5997,7 +6156,7 @@
         <v>40</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>182</v>
@@ -6018,7 +6177,7 @@
         <v>182</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>40</v>
@@ -6044,9 +6203,12 @@
       <c r="V77" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="W77" s="2"/>
-    </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="W77" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X77" s="2"/>
+    </row>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
         <v>49</v>
       </c>
@@ -6060,7 +6222,7 @@
         <v>49</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>174</v>
@@ -6081,7 +6243,7 @@
         <v>174</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>49</v>
@@ -6107,17 +6269,20 @@
       <c r="V78" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W78" s="2"/>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="E79" s="1" t="s">
+      <c r="W78" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X78" s="2"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="C79" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>180</v>
@@ -6138,7 +6303,7 @@
         <v>180</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="O79" s="1" t="s">
         <v>67</v>
@@ -6164,10 +6329,13 @@
       <c r="V79" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W79" s="2"/>
-    </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="E80" s="1" t="s">
+      <c r="W79" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="X79" s="2"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="C80" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -6221,10 +6389,13 @@
       <c r="V80" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E81" s="1" t="s">
+      <c r="W80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X80" s="2"/>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C81" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -6278,10 +6449,13 @@
       <c r="V81" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W81" s="2"/>
-    </row>
-    <row r="82" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E82" s="1" t="s">
+      <c r="W81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="X81" s="2"/>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C82" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -6335,12 +6509,12 @@
       <c r="V82" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="W82" s="2"/>
-    </row>
-    <row r="83" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G83" s="1" t="s">
-        <v>186</v>
-      </c>
+      <c r="W82" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="X82" s="2"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H83" s="1" t="s">
         <v>186</v>
       </c>
@@ -6359,7 +6533,7 @@
       <c r="M83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="O83" s="1" t="s">
+      <c r="N83" s="1" t="s">
         <v>186</v>
       </c>
       <c r="P83" s="1" t="s">
@@ -6383,12 +6557,12 @@
       <c r="V83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="W83" s="2"/>
-    </row>
-    <row r="84" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G84" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="W83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="X83" s="2"/>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H84" s="1" t="s">
         <v>112</v>
       </c>
@@ -6407,7 +6581,7 @@
       <c r="M84" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="O84" s="1" t="s">
+      <c r="N84" s="1" t="s">
         <v>112</v>
       </c>
       <c r="P84" s="1" t="s">
@@ -6431,15 +6605,15 @@
       <c r="V84" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W84" s="2"/>
-      <c r="X84" s="1" t="s">
+      <c r="W84" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X84" s="2"/>
+      <c r="Y84" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="85" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G85" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H85" s="1" t="s">
         <v>128</v>
       </c>
@@ -6458,7 +6632,7 @@
       <c r="M85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="O85" s="1" t="s">
+      <c r="N85" s="1" t="s">
         <v>128</v>
       </c>
       <c r="P85" s="1" t="s">
@@ -6482,13 +6656,16 @@
       <c r="V85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="W85" s="2"/>
-      <c r="X85" s="1" t="s">
+      <c r="W85" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X85" s="2"/>
+      <c r="Y85" s="1" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="86" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E86" s="1" t="s">
+    <row r="86" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C86" s="1" t="s">
         <v>72</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -6542,17 +6719,20 @@
       <c r="V86" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="W86" s="2"/>
-    </row>
-    <row r="87" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E87" s="1" t="s">
+      <c r="W86" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X86" s="2"/>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C87" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>71</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>183</v>
@@ -6573,7 +6753,7 @@
         <v>183</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>71</v>
@@ -6599,10 +6779,13 @@
       <c r="V87" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="W87" s="2"/>
-    </row>
-    <row r="88" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E88" s="1" t="s">
+      <c r="W87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="X87" s="2"/>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C88" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -6614,7 +6797,7 @@
       <c r="H88" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K88" s="1" t="s">
@@ -6653,10 +6836,13 @@
       <c r="V88" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="W88" s="2"/>
-    </row>
-    <row r="89" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E89" s="1" t="s">
+      <c r="W88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X88" s="2"/>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C89" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -6710,17 +6896,20 @@
       <c r="V89" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="W89" s="2"/>
-    </row>
-    <row r="90" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E90" s="1" t="s">
-        <v>64</v>
+      <c r="W89" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="X89" s="2"/>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C90" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>116</v>
@@ -6741,7 +6930,7 @@
         <v>116</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>64</v>
@@ -6767,10 +6956,13 @@
       <c r="V90" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="W90" s="2"/>
-    </row>
-    <row r="91" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E91" s="1" t="s">
+      <c r="W90" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="X90" s="2"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C91" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -6824,17 +7016,20 @@
       <c r="V91" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="W91" s="2"/>
-    </row>
-    <row r="92" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E92" s="1" t="s">
+      <c r="W91" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X91" s="2"/>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C92" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>141</v>
@@ -6855,7 +7050,7 @@
         <v>141</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>74</v>
@@ -6881,10 +7076,13 @@
       <c r="V92" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="W92" s="2"/>
-    </row>
-    <row r="93" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E93" s="1" t="s">
+      <c r="W92" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="X92" s="2"/>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C93" s="1" t="s">
         <v>75</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -6938,17 +7136,20 @@
       <c r="V93" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="W93" s="2"/>
-    </row>
-    <row r="94" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E94" s="1" t="s">
+      <c r="W93" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="X93" s="2"/>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C94" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>176</v>
@@ -6969,7 +7170,7 @@
         <v>176</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>70</v>
@@ -6995,17 +7196,20 @@
       <c r="V94" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W94" s="2"/>
-    </row>
-    <row r="95" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E95" s="1" t="s">
+      <c r="W94" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="X94" s="2"/>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C95" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>76</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>148</v>
@@ -7026,7 +7230,7 @@
         <v>148</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>76</v>
@@ -7052,17 +7256,20 @@
       <c r="V95" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="W95" s="2"/>
-    </row>
-    <row r="96" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E96" s="1" t="s">
+      <c r="W95" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="X95" s="2"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>140</v>
@@ -7083,7 +7290,7 @@
         <v>140</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>69</v>
@@ -7109,17 +7316,20 @@
       <c r="V96" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="W96" s="2"/>
-    </row>
-    <row r="97" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E97" s="1" t="s">
+      <c r="W96" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X96" s="2"/>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C97" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>161</v>
@@ -7140,7 +7350,7 @@
         <v>161</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>68</v>
@@ -7166,17 +7376,20 @@
       <c r="V97" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="W97" s="2"/>
-    </row>
-    <row r="98" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E98" s="1" t="s">
+      <c r="W97" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="X97" s="2"/>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C98" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>55</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>158</v>
@@ -7197,7 +7410,7 @@
         <v>158</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>55</v>
@@ -7223,17 +7436,20 @@
       <c r="V98" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="W98" s="2"/>
-    </row>
-    <row r="99" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E99" s="1" t="s">
+      <c r="W98" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X98" s="2"/>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C99" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>153</v>
@@ -7254,7 +7470,7 @@
         <v>153</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>51</v>
@@ -7280,17 +7496,20 @@
       <c r="V99" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="W99" s="2"/>
-    </row>
-    <row r="100" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E100" s="1" t="s">
+      <c r="W99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X99" s="2"/>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C100" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>65</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>127</v>
@@ -7311,7 +7530,7 @@
         <v>127</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>65</v>
@@ -7337,17 +7556,20 @@
       <c r="V100" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W100" s="2"/>
-    </row>
-    <row r="101" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E101" s="1" t="s">
+      <c r="W100" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X100" s="2"/>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C101" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>201</v>
@@ -7356,7 +7578,7 @@
         <v>201</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>53</v>
@@ -7394,24 +7616,24 @@
       <c r="V101" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="W101" s="2"/>
-    </row>
-    <row r="102" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="N102" s="1" t="s">
+      <c r="W101" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X101" s="2"/>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="O102" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="W102" s="2"/>
-    </row>
-    <row r="103" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="N103" s="1" t="s">
+      <c r="X102" s="2"/>
+    </row>
+    <row r="103" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="O103" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="W103" s="2"/>
-    </row>
-    <row r="104" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="O104" s="1" t="s">
-        <v>254</v>
-      </c>
+      <c r="X103" s="2"/>
+    </row>
+    <row r="104" spans="3:25" x14ac:dyDescent="0.3">
       <c r="P104" s="1" t="s">
         <v>254</v>
       </c>
@@ -7433,12 +7655,12 @@
       <c r="V104" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="W104" s="2"/>
-    </row>
-    <row r="105" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="O105" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="W104" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="X104" s="2"/>
+    </row>
+    <row r="105" spans="3:25" x14ac:dyDescent="0.3">
       <c r="P105" s="1" t="s">
         <v>265</v>
       </c>
@@ -7460,12 +7682,12 @@
       <c r="V105" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="W105" s="2"/>
-    </row>
-    <row r="106" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G106" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="W105" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="X105" s="2"/>
+    </row>
+    <row r="106" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H106" s="1" t="s">
         <v>144</v>
       </c>
@@ -7484,7 +7706,7 @@
       <c r="M106" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="O106" s="1" t="s">
+      <c r="N106" s="1" t="s">
         <v>144</v>
       </c>
       <c r="P106" s="1" t="s">
@@ -7508,12 +7730,12 @@
       <c r="V106" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W106" s="2"/>
-    </row>
-    <row r="107" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G107" s="1" t="s">
-        <v>117</v>
-      </c>
+      <c r="W106" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="X106" s="2"/>
+    </row>
+    <row r="107" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H107" s="1" t="s">
         <v>117</v>
       </c>
@@ -7532,8 +7754,8 @@
       <c r="M107" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O107" s="1" t="s">
-        <v>258</v>
+      <c r="N107" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="P107" s="1" t="s">
         <v>258</v>
@@ -7556,15 +7778,15 @@
       <c r="V107" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="W107" s="2"/>
-      <c r="X107" s="1" t="s">
+      <c r="W107" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="X107" s="2"/>
+      <c r="Y107" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="108" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G108" s="1" t="s">
-        <v>122</v>
-      </c>
+    <row r="108" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H108" s="1" t="s">
         <v>122</v>
       </c>
@@ -7583,8 +7805,8 @@
       <c r="M108" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="O108" s="1" t="s">
-        <v>259</v>
+      <c r="N108" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="P108" s="1" t="s">
         <v>259</v>
@@ -7607,15 +7829,15 @@
       <c r="V108" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="W108" s="2"/>
-      <c r="X108" s="1" t="s">
+      <c r="W108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="X108" s="2"/>
+      <c r="Y108" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="109" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G109" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="109" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H109" s="1" t="s">
         <v>156</v>
       </c>
@@ -7634,8 +7856,8 @@
       <c r="M109" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="O109" s="1" t="s">
-        <v>262</v>
+      <c r="N109" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="P109" s="1" t="s">
         <v>262</v>
@@ -7658,15 +7880,15 @@
       <c r="V109" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="W109" s="2"/>
-      <c r="X109" s="1" t="s">
+      <c r="W109" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="X109" s="2"/>
+      <c r="Y109" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="110" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G110" s="1" t="s">
-        <v>199</v>
-      </c>
+    <row r="110" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H110" s="1" t="s">
         <v>199</v>
       </c>
@@ -7674,7 +7896,7 @@
         <v>199</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K110" s="1" t="s">
         <v>202</v>
@@ -7685,7 +7907,7 @@
       <c r="M110" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="O110" s="1" t="s">
+      <c r="N110" s="1" t="s">
         <v>202</v>
       </c>
       <c r="P110" s="1" t="s">
@@ -7709,12 +7931,12 @@
       <c r="V110" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="W110" s="2"/>
-    </row>
-    <row r="111" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G111" s="1" t="s">
-        <v>177</v>
-      </c>
+      <c r="W110" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="X110" s="2"/>
+    </row>
+    <row r="111" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H111" s="1" t="s">
         <v>177</v>
       </c>
@@ -7733,7 +7955,7 @@
       <c r="M111" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="O111" s="1" t="s">
+      <c r="N111" s="1" t="s">
         <v>177</v>
       </c>
       <c r="P111" s="1" t="s">
@@ -7757,12 +7979,12 @@
       <c r="V111" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="W111" s="2"/>
-    </row>
-    <row r="112" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G112" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="W111" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="X111" s="2"/>
+    </row>
+    <row r="112" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H112" s="1" t="s">
         <v>125</v>
       </c>
@@ -7781,7 +8003,7 @@
       <c r="M112" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O112" s="1" t="s">
+      <c r="N112" s="1" t="s">
         <v>125</v>
       </c>
       <c r="P112" s="1" t="s">
@@ -7805,12 +8027,12 @@
       <c r="V112" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="W112" s="2"/>
-    </row>
-    <row r="113" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G113" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="W112" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="X112" s="2"/>
+    </row>
+    <row r="113" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H113" s="1" t="s">
         <v>91</v>
       </c>
@@ -7829,7 +8051,7 @@
       <c r="M113" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O113" s="1" t="s">
+      <c r="N113" s="1" t="s">
         <v>91</v>
       </c>
       <c r="P113" s="1" t="s">
@@ -7853,15 +8075,15 @@
       <c r="V113" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="W113" s="2"/>
-      <c r="X113" s="1" t="s">
+      <c r="W113" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X113" s="2"/>
+      <c r="Y113" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G114" s="1" t="s">
-        <v>92</v>
-      </c>
+    <row r="114" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H114" s="1" t="s">
         <v>92</v>
       </c>
@@ -7880,7 +8102,7 @@
       <c r="M114" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O114" s="1" t="s">
+      <c r="N114" s="1" t="s">
         <v>92</v>
       </c>
       <c r="P114" s="1" t="s">
@@ -7904,15 +8126,15 @@
       <c r="V114" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W114" s="2"/>
-      <c r="X114" s="1" t="s">
+      <c r="W114" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="X114" s="2"/>
+      <c r="Y114" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="115" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G115" s="1" t="s">
-        <v>90</v>
-      </c>
+    <row r="115" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H115" s="1" t="s">
         <v>90</v>
       </c>
@@ -7931,7 +8153,7 @@
       <c r="M115" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O115" s="1" t="s">
+      <c r="N115" s="1" t="s">
         <v>90</v>
       </c>
       <c r="P115" s="1" t="s">
@@ -7955,15 +8177,15 @@
       <c r="V115" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="W115" s="2"/>
-      <c r="X115" s="1" t="s">
+      <c r="W115" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="X115" s="2"/>
+      <c r="Y115" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="116" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G116" s="1" t="s">
-        <v>101</v>
-      </c>
+    <row r="116" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H116" s="1" t="s">
         <v>101</v>
       </c>
@@ -7982,8 +8204,8 @@
       <c r="M116" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O116" s="1" t="s">
-        <v>257</v>
+      <c r="N116" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="P116" s="1" t="s">
         <v>257</v>
@@ -8006,12 +8228,12 @@
       <c r="V116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="W116" s="2"/>
-    </row>
-    <row r="117" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G117" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="W116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="X116" s="2"/>
+    </row>
+    <row r="117" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H117" s="1" t="s">
         <v>99</v>
       </c>
@@ -8030,7 +8252,7 @@
       <c r="M117" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="O117" s="1" t="s">
+      <c r="N117" s="1" t="s">
         <v>99</v>
       </c>
       <c r="P117" s="1" t="s">
@@ -8054,12 +8276,12 @@
       <c r="V117" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="W117" s="2"/>
-    </row>
-    <row r="118" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G118" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="W117" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="X117" s="2"/>
+    </row>
+    <row r="118" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H118" s="1" t="s">
         <v>100</v>
       </c>
@@ -8078,7 +8300,7 @@
       <c r="M118" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="O118" s="1" t="s">
+      <c r="N118" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P118" s="1" t="s">
@@ -8102,12 +8324,12 @@
       <c r="V118" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="W118" s="2"/>
-    </row>
-    <row r="119" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="G119" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="W118" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="X118" s="2"/>
+    </row>
+    <row r="119" spans="3:25" x14ac:dyDescent="0.3">
       <c r="H119" s="1" t="s">
         <v>98</v>
       </c>
@@ -8126,7 +8348,7 @@
       <c r="M119" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O119" s="1" t="s">
+      <c r="N119" s="1" t="s">
         <v>98</v>
       </c>
       <c r="P119" s="1" t="s">
@@ -8150,12 +8372,12 @@
       <c r="V119" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="W119" s="2"/>
-    </row>
-    <row r="120" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I120" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="W119" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="X119" s="2"/>
+    </row>
+    <row r="120" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J120" s="1" t="s">
         <v>95</v>
       </c>
@@ -8168,7 +8390,7 @@
       <c r="M120" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O120" s="1" t="s">
+      <c r="N120" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P120" s="1" t="s">
@@ -8192,15 +8414,15 @@
       <c r="V120" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="W120" s="2"/>
-      <c r="X120" s="1" t="s">
+      <c r="W120" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="X120" s="2"/>
+      <c r="Y120" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="121" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I121" s="1" t="s">
-        <v>94</v>
-      </c>
+    <row r="121" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J121" s="1" t="s">
         <v>94</v>
       </c>
@@ -8213,7 +8435,7 @@
       <c r="M121" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="O121" s="1" t="s">
+      <c r="N121" s="1" t="s">
         <v>94</v>
       </c>
       <c r="P121" s="1" t="s">
@@ -8237,15 +8459,15 @@
       <c r="V121" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="W121" s="2"/>
-      <c r="X121" s="1" t="s">
+      <c r="W121" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="X121" s="2"/>
+      <c r="Y121" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="122" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I122" s="1" t="s">
-        <v>93</v>
-      </c>
+    <row r="122" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J122" s="1" t="s">
         <v>93</v>
       </c>
@@ -8258,7 +8480,7 @@
       <c r="M122" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="O122" s="1" t="s">
+      <c r="N122" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P122" s="1" t="s">
@@ -8282,15 +8504,15 @@
       <c r="V122" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="W122" s="2"/>
-      <c r="X122" s="1" t="s">
+      <c r="W122" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X122" s="2"/>
+      <c r="Y122" s="1" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="123" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I123" s="1" t="s">
-        <v>147</v>
-      </c>
+    <row r="123" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J123" s="1" t="s">
         <v>147</v>
       </c>
@@ -8303,7 +8525,7 @@
       <c r="M123" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="O123" s="1" t="s">
+      <c r="N123" s="1" t="s">
         <v>147</v>
       </c>
       <c r="P123" s="1" t="s">
@@ -8327,15 +8549,15 @@
       <c r="V123" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="W123" s="2"/>
-      <c r="X123" s="1" t="s">
+      <c r="W123" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="X123" s="2"/>
+      <c r="Y123" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="124" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I124" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="124" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J124" s="1" t="s">
         <v>146</v>
       </c>
@@ -8348,7 +8570,7 @@
       <c r="M124" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="O124" s="1" t="s">
+      <c r="N124" s="1" t="s">
         <v>146</v>
       </c>
       <c r="P124" s="1" t="s">
@@ -8372,15 +8594,15 @@
       <c r="V124" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="W124" s="2"/>
-      <c r="X124" s="1" t="s">
+      <c r="W124" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="X124" s="2"/>
+      <c r="Y124" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="125" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="I125" s="1" t="s">
-        <v>145</v>
-      </c>
+    <row r="125" spans="3:25" x14ac:dyDescent="0.3">
       <c r="J125" s="1" t="s">
         <v>145</v>
       </c>
@@ -8393,7 +8615,7 @@
       <c r="M125" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="O125" s="1" t="s">
+      <c r="N125" s="1" t="s">
         <v>145</v>
       </c>
       <c r="P125" s="1" t="s">
@@ -8417,20 +8639,23 @@
       <c r="V125" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="W125" s="2"/>
-      <c r="X125" s="1" t="s">
+      <c r="W125" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="X125" s="2"/>
+      <c r="Y125" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="126" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E126" s="1" t="s">
+    <row r="126" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C126" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>150</v>
@@ -8451,7 +8676,7 @@
         <v>150</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="O126" s="1" t="s">
         <v>52</v>
@@ -8471,27 +8696,27 @@
       <c r="T126" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="U126" s="2"/>
-      <c r="W126" s="2"/>
-      <c r="X126" s="1" t="s">
+      <c r="U126" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V126" s="2"/>
+      <c r="X126" s="2"/>
+      <c r="Y126" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="127" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E127" s="1" t="s">
-        <v>57</v>
-      </c>
+    <row r="127" spans="3:25" x14ac:dyDescent="0.3">
       <c r="F127" s="1" t="s">
         <v>57</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J127" s="1" t="s">
-        <v>57</v>
+      <c r="I127" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="K127" s="1" t="s">
         <v>57</v>
@@ -8499,16 +8724,16 @@
       <c r="L127" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N127" s="1" t="s">
+      <c r="M127" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U127" s="2"/>
-      <c r="W127" s="2"/>
-    </row>
-    <row r="128" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E128" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="O127" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="V127" s="2"/>
+      <c r="X127" s="2"/>
+    </row>
+    <row r="128" spans="3:25" x14ac:dyDescent="0.3">
       <c r="F128" s="1" t="s">
         <v>58</v>
       </c>
@@ -8518,7 +8743,7 @@
       <c r="H128" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>58</v>
       </c>
       <c r="K128" s="1" t="s">
@@ -8527,33 +8752,33 @@
       <c r="L128" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N128" s="1" t="s">
+      <c r="M128" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U128" s="2"/>
-      <c r="W128" s="2"/>
-    </row>
-    <row r="129" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="J129" s="1" t="s">
+      <c r="O128" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V128" s="2"/>
+      <c r="X128" s="2"/>
+    </row>
+    <row r="129" spans="9:25" x14ac:dyDescent="0.3">
+      <c r="K129" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="U129" s="2"/>
-      <c r="W129" s="2"/>
-    </row>
-    <row r="130" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I130" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="V129" s="2"/>
+      <c r="X129" s="2"/>
+    </row>
+    <row r="130" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J130" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="L130" s="1" t="s">
+      <c r="K130" s="1" t="s">
         <v>132</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="O130" s="1" t="s">
+      <c r="N130" s="1" t="s">
         <v>132</v>
       </c>
       <c r="P130" s="1" t="s">
@@ -8577,12 +8802,12 @@
       <c r="V130" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="W130" s="2"/>
-    </row>
-    <row r="131" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I131" s="1" t="s">
-        <v>172</v>
-      </c>
+      <c r="W130" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="X130" s="2"/>
+    </row>
+    <row r="131" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J131" s="1" t="s">
         <v>172</v>
       </c>
@@ -8595,7 +8820,7 @@
       <c r="M131" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="O131" s="1" t="s">
+      <c r="N131" s="1" t="s">
         <v>172</v>
       </c>
       <c r="P131" s="1" t="s">
@@ -8619,12 +8844,12 @@
       <c r="V131" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="W131" s="2"/>
-    </row>
-    <row r="132" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I132" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="W131" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="X131" s="2"/>
+    </row>
+    <row r="132" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J132" s="1" t="s">
         <v>143</v>
       </c>
@@ -8637,7 +8862,7 @@
       <c r="M132" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="O132" s="1" t="s">
+      <c r="N132" s="1" t="s">
         <v>143</v>
       </c>
       <c r="P132" s="1" t="s">
@@ -8661,12 +8886,12 @@
       <c r="V132" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="W132" s="2"/>
-    </row>
-    <row r="133" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="O133" s="1" t="s">
-        <v>255</v>
-      </c>
+      <c r="W132" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="X132" s="2"/>
+    </row>
+    <row r="133" spans="9:25" x14ac:dyDescent="0.3">
       <c r="P133" s="1" t="s">
         <v>255</v>
       </c>
@@ -8688,12 +8913,12 @@
       <c r="V133" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="W133" s="2"/>
-    </row>
-    <row r="134" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="O134" s="1" t="s">
-        <v>256</v>
-      </c>
+      <c r="W133" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="X133" s="2"/>
+    </row>
+    <row r="134" spans="9:25" x14ac:dyDescent="0.3">
       <c r="P134" s="1" t="s">
         <v>256</v>
       </c>
@@ -8715,12 +8940,12 @@
       <c r="V134" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="W134" s="2"/>
-    </row>
-    <row r="135" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="H135" s="1" t="s">
-        <v>151</v>
-      </c>
+      <c r="W134" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="X134" s="2"/>
+    </row>
+    <row r="135" spans="9:25" x14ac:dyDescent="0.3">
       <c r="I135" s="1" t="s">
         <v>151</v>
       </c>
@@ -8736,7 +8961,7 @@
       <c r="M135" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O135" s="1" t="s">
+      <c r="N135" s="1" t="s">
         <v>151</v>
       </c>
       <c r="P135" s="1" t="s">
@@ -8760,15 +8985,15 @@
       <c r="V135" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="W135" s="2"/>
-      <c r="X135" s="1" t="s">
+      <c r="W135" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="X135" s="2"/>
+      <c r="Y135" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="136" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I136" s="1" t="s">
-        <v>129</v>
-      </c>
+    <row r="136" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J136" s="1" t="s">
         <v>129</v>
       </c>
@@ -8781,7 +9006,7 @@
       <c r="M136" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O136" s="1" t="s">
+      <c r="N136" s="1" t="s">
         <v>129</v>
       </c>
       <c r="P136" s="1" t="s">
@@ -8805,15 +9030,15 @@
       <c r="V136" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W136" s="2"/>
-      <c r="X136" s="1" t="s">
+      <c r="W136" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X136" s="2"/>
+      <c r="Y136" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="137" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I137" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="137" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J137" s="1" t="s">
         <v>115</v>
       </c>
@@ -8826,7 +9051,7 @@
       <c r="M137" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="O137" s="1" t="s">
+      <c r="N137" s="1" t="s">
         <v>115</v>
       </c>
       <c r="P137" s="1" t="s">
@@ -8850,15 +9075,15 @@
       <c r="V137" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="W137" s="2"/>
-      <c r="X137" s="1" t="s">
+      <c r="W137" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="X137" s="2"/>
+      <c r="Y137" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="138" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I138" s="1" t="s">
-        <v>155</v>
-      </c>
+    <row r="138" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J138" s="1" t="s">
         <v>155</v>
       </c>
@@ -8898,12 +9123,12 @@
       <c r="V138" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="W138" s="2"/>
-    </row>
-    <row r="139" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I139" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="W138" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X138" s="2"/>
+    </row>
+    <row r="139" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J139" s="1" t="s">
         <v>89</v>
       </c>
@@ -8916,7 +9141,7 @@
       <c r="M139" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O139" s="1" t="s">
+      <c r="N139" s="1" t="s">
         <v>89</v>
       </c>
       <c r="P139" s="1" t="s">
@@ -8940,14 +9165,14 @@
       <c r="V139" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="W139" s="2"/>
-    </row>
-    <row r="140" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I140" s="1" t="s">
+      <c r="W139" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X139" s="2"/>
+    </row>
+    <row r="140" spans="9:25" x14ac:dyDescent="0.3">
+      <c r="J140" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="K140" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>220</v>
@@ -8955,7 +9180,7 @@
       <c r="M140" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="O140" s="1" t="s">
+      <c r="N140" s="1" t="s">
         <v>220</v>
       </c>
       <c r="P140" s="1" t="s">
@@ -8979,15 +9204,15 @@
       <c r="V140" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="W140" s="2"/>
-      <c r="X140" s="9" t="s">
+      <c r="W140" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="X140" s="2"/>
+      <c r="Y140" s="9" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="141" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I141" s="1" t="s">
-        <v>111</v>
-      </c>
+    <row r="141" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J141" s="1" t="s">
         <v>111</v>
       </c>
@@ -9000,7 +9225,7 @@
       <c r="M141" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="O141" s="1" t="s">
+      <c r="N141" s="1" t="s">
         <v>111</v>
       </c>
       <c r="P141" s="1" t="s">
@@ -9024,12 +9249,12 @@
       <c r="V141" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="W141" s="2"/>
-    </row>
-    <row r="142" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I142" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="W141" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="X141" s="2"/>
+    </row>
+    <row r="142" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J142" s="1" t="s">
         <v>139</v>
       </c>
@@ -9042,7 +9267,7 @@
       <c r="M142" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="O142" s="1" t="s">
+      <c r="N142" s="1" t="s">
         <v>139</v>
       </c>
       <c r="P142" s="1" t="s">
@@ -9066,15 +9291,15 @@
       <c r="V142" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="W142" s="2"/>
-      <c r="X142" s="1" t="s">
+      <c r="W142" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="X142" s="2"/>
+      <c r="Y142" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="143" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I143" s="1" t="s">
-        <v>142</v>
-      </c>
+    <row r="143" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J143" s="1" t="s">
         <v>142</v>
       </c>
@@ -9087,7 +9312,7 @@
       <c r="M143" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="O143" s="1" t="s">
+      <c r="N143" s="1" t="s">
         <v>142</v>
       </c>
       <c r="P143" s="1" t="s">
@@ -9105,21 +9330,21 @@
       <c r="T143" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="U143" s="6" t="s">
+      <c r="U143" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="V143" s="1" t="s">
+      <c r="V143" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="W143" s="2"/>
-      <c r="X143" s="9" t="s">
+      <c r="W143" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="X143" s="2"/>
+      <c r="Y143" s="9" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="144" spans="8:24" x14ac:dyDescent="0.3">
-      <c r="I144" s="1" t="s">
-        <v>114</v>
-      </c>
+    <row r="144" spans="9:25" x14ac:dyDescent="0.3">
       <c r="J144" s="1" t="s">
         <v>114</v>
       </c>
@@ -9132,7 +9357,7 @@
       <c r="M144" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O144" s="1" t="s">
+      <c r="N144" s="1" t="s">
         <v>114</v>
       </c>
       <c r="P144" s="1" t="s">
@@ -9156,15 +9381,15 @@
       <c r="V144" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="W144" s="2"/>
-      <c r="X144" s="1" t="s">
+      <c r="W144" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="X144" s="2"/>
+      <c r="Y144" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="145" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="I145" s="1" t="s">
-        <v>133</v>
-      </c>
+    <row r="145" spans="8:25" x14ac:dyDescent="0.3">
       <c r="J145" s="1" t="s">
         <v>133</v>
       </c>
@@ -9177,7 +9402,7 @@
       <c r="M145" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="O145" s="1" t="s">
+      <c r="N145" s="1" t="s">
         <v>133</v>
       </c>
       <c r="P145" s="1" t="s">
@@ -9201,15 +9426,15 @@
       <c r="V145" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="W145" s="2"/>
-      <c r="X145" s="9" t="s">
+      <c r="W145" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="X145" s="2"/>
+      <c r="Y145" s="9" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="146" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="I146" s="1" t="s">
-        <v>168</v>
-      </c>
+    <row r="146" spans="8:25" x14ac:dyDescent="0.3">
       <c r="J146" s="1" t="s">
         <v>168</v>
       </c>
@@ -9222,7 +9447,7 @@
       <c r="M146" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="O146" s="1" t="s">
+      <c r="N146" s="1" t="s">
         <v>168</v>
       </c>
       <c r="P146" s="1" t="s">
@@ -9246,12 +9471,12 @@
       <c r="V146" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="W146" s="2"/>
-    </row>
-    <row r="147" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="I147" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="W146" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="X146" s="2"/>
+    </row>
+    <row r="147" spans="8:25" x14ac:dyDescent="0.3">
       <c r="J147" s="1" t="s">
         <v>121</v>
       </c>
@@ -9264,7 +9489,7 @@
       <c r="M147" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O147" s="1" t="s">
+      <c r="N147" s="1" t="s">
         <v>121</v>
       </c>
       <c r="P147" s="1" t="s">
@@ -9288,12 +9513,12 @@
       <c r="V147" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="W147" s="2"/>
-    </row>
-    <row r="148" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="I148" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="W147" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X147" s="2"/>
+    </row>
+    <row r="148" spans="8:25" x14ac:dyDescent="0.3">
       <c r="J148" s="1" t="s">
         <v>157</v>
       </c>
@@ -9306,7 +9531,7 @@
       <c r="M148" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="O148" s="1" t="s">
+      <c r="N148" s="1" t="s">
         <v>157</v>
       </c>
       <c r="P148" s="1" t="s">
@@ -9330,483 +9555,486 @@
       <c r="V148" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="W148" s="2"/>
-    </row>
-    <row r="149" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="G149" s="1" t="s">
-        <v>205</v>
-      </c>
+      <c r="W148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="X148" s="2"/>
+    </row>
+    <row r="149" spans="8:25" x14ac:dyDescent="0.3">
       <c r="H149" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="I149" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="N149" s="1" t="s">
+      <c r="K149" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O149" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="U149" s="6" t="s">
+      <c r="V149" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="V149" s="1" t="s">
+      <c r="W149" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="W149" s="2"/>
-    </row>
-    <row r="150" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="N150" s="1" t="s">
+      <c r="X149" s="2"/>
+    </row>
+    <row r="150" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="O150" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="U150" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="V150" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="W150" s="2"/>
-      <c r="X150" s="1" t="s">
+      <c r="W150" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="X150" s="2"/>
+      <c r="Y150" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="151" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="U151" s="1" t="s">
-        <v>293</v>
-      </c>
+    <row r="151" spans="8:25" x14ac:dyDescent="0.3">
       <c r="V151" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="W151" s="2"/>
-      <c r="X151" s="1" t="s">
+      <c r="W151" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="X151" s="2"/>
+      <c r="Y151" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="152" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="W152" s="2"/>
-    </row>
-    <row r="153" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="U153" s="1" t="s">
+    <row r="152" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="X152" s="2"/>
+    </row>
+    <row r="153" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="V153" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="W153" s="2"/>
-      <c r="X153" s="1" t="s">
+      <c r="X153" s="2"/>
+      <c r="Y153" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="154" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="U154" s="1" t="s">
+    <row r="154" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="V154" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="X154" s="1" t="s">
+      <c r="Y154" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="155" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="I155" s="1" t="s">
-        <v>203</v>
-      </c>
+    <row r="155" spans="8:25" x14ac:dyDescent="0.3">
       <c r="J155" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="U155" s="1" t="s">
+      <c r="K155" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="W155" s="2"/>
-      <c r="X155" s="1" t="s">
+      <c r="V155" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="X155" s="2"/>
+      <c r="Y155" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="156" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="J156" s="1" t="s">
+    <row r="156" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="K156" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="W156" s="2"/>
-      <c r="X156" s="1" t="s">
+      <c r="X156" s="2"/>
+      <c r="Y156" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="157" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="J157" s="1" t="s">
+    <row r="157" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="K157" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="W157" s="2"/>
-      <c r="X157" s="1" t="s">
+      <c r="X157" s="2"/>
+      <c r="Y157" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="158" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="J158" s="1" t="s">
+    <row r="158" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="K158" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="W158" s="2"/>
-      <c r="X158" s="1" t="s">
+      <c r="X158" s="2"/>
+      <c r="Y158" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="159" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="J159" s="1" t="s">
+    <row r="159" spans="8:25" x14ac:dyDescent="0.3">
+      <c r="K159" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="W159" s="2"/>
-      <c r="X159" s="1" t="s">
+      <c r="X159" s="2"/>
+      <c r="Y159" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="160" spans="7:24" x14ac:dyDescent="0.3">
-      <c r="U160" s="1" t="s">
-        <v>304</v>
-      </c>
+    <row r="160" spans="8:25" x14ac:dyDescent="0.3">
       <c r="V160" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="W160" s="2"/>
-    </row>
-    <row r="161" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U161" s="1" t="s">
+      <c r="W160" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="X160" s="2"/>
+    </row>
+    <row r="161" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="V161" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="W161" s="2"/>
-    </row>
-    <row r="162" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U162" s="1" t="s">
-        <v>305</v>
-      </c>
+      <c r="X161" s="2"/>
+    </row>
+    <row r="162" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V162" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="W162" s="2"/>
-    </row>
-    <row r="163" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U163" s="1" t="s">
-        <v>299</v>
-      </c>
+      <c r="W162" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="X162" s="2"/>
+    </row>
+    <row r="163" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V163" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="W163" s="2"/>
-      <c r="X163" s="1" t="s">
+      <c r="W163" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="X163" s="2"/>
+      <c r="Y163" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="164" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U164" s="1" t="s">
-        <v>287</v>
-      </c>
+    <row r="164" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V164" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="165" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U165" s="1" t="s">
-        <v>302</v>
-      </c>
+      <c r="W164" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="165" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V165" s="1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="166" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="V166" s="1" t="s">
+      <c r="W165" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="166" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="W166" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="167" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U167" s="1" t="s">
+    <row r="167" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="V167" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="W167" s="2"/>
-      <c r="X167" s="1" t="s">
+      <c r="X167" s="2"/>
+      <c r="Y167" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="168" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U168" s="1" t="s">
+    <row r="168" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="V168" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="W168" s="2"/>
-      <c r="X168" s="1" t="s">
+      <c r="X168" s="2"/>
+      <c r="Y168" s="1" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="169" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U169" s="1" t="s">
-        <v>215</v>
-      </c>
+    <row r="169" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V169" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="W169" s="2"/>
-      <c r="X169" s="1" t="s">
+      <c r="W169" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="X169" s="2"/>
+      <c r="Y169" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="170" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U170" s="1" t="s">
-        <v>290</v>
-      </c>
+    <row r="170" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V170" s="1" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="171" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U171" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="W170" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="171" spans="15:25" x14ac:dyDescent="0.3">
       <c r="V171" s="1" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="172" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="N172" s="1" t="s">
+      <c r="W171" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="172" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="O172" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="U172" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="V172" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="W172" s="2"/>
-    </row>
-    <row r="173" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="U173" s="1" t="s">
+      <c r="W172" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="X172" s="2"/>
+    </row>
+    <row r="173" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="V173" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="X173" s="1" t="s">
+      <c r="Y173" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="174" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="N174" s="1" t="s">
+    <row r="174" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="O174" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="U174" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="V174" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="X174" s="1" t="s">
+      <c r="W174" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y174" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="175" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="N175" s="1" t="s">
+    <row r="175" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="O175" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="U175" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="V175" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="X175" s="1" t="s">
+      <c r="W175" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y175" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="176" spans="14:24" x14ac:dyDescent="0.3">
-      <c r="N176" s="1" t="s">
+    <row r="176" spans="15:25" x14ac:dyDescent="0.3">
+      <c r="O176" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="U176" s="6" t="s">
+      <c r="V176" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="V176" s="1" t="s">
+      <c r="W176" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="W176" s="2"/>
-      <c r="X176" s="1" t="s">
+      <c r="X176" s="2"/>
+      <c r="Y176" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="177" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="U177" s="1" t="s">
-        <v>298</v>
-      </c>
+    <row r="177" spans="20:25" x14ac:dyDescent="0.3">
       <c r="V177" s="1" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="178" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="U178" s="1" t="s">
+      <c r="W177" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="178" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="V178" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="X178" s="1" t="s">
+      <c r="Y178" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="179" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="S179" s="1" t="s">
+    <row r="179" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="T179" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="V179" s="1" t="s">
+      <c r="W179" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="180" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V180" s="1" t="s">
+    <row r="180" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W180" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="X180" s="1" t="s">
+      <c r="Y180" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="181" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V181" s="1" t="s">
+    <row r="181" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W181" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="182" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V182" s="1" t="s">
+    <row r="182" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W182" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="X182" s="1" t="s">
+      <c r="Y182" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="183" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V183" s="1" t="s">
+    <row r="183" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W183" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="X183" s="1" t="s">
+      <c r="Y183" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="184" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V184" s="1" t="s">
+    <row r="184" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W184" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="X184" s="1" t="s">
+      <c r="Y184" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="185" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="U185" s="1" t="s">
+    <row r="185" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="V185" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="X185" s="1" t="s">
+      <c r="Y185" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="186" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="U186" s="1" t="s">
+    <row r="186" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="V186" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="X186" s="1" t="s">
+      <c r="Y186" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="187" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="U187" s="1" t="s">
-        <v>327</v>
-      </c>
+    <row r="187" spans="20:25" x14ac:dyDescent="0.3">
       <c r="V187" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="X187" s="1" t="s">
+      <c r="W187" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y187" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V188" s="1" t="s">
+    <row r="188" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W188" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="X188" s="1" t="s">
+      <c r="Y188" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="189" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V189" s="1" t="s">
+    <row r="189" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W189" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="X189" s="1" t="s">
+      <c r="Y189" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V190" s="1" t="s">
+    <row r="190" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W190" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="X190" s="1" t="s">
+      <c r="Y190" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V191" s="1" t="s">
+    <row r="191" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W191" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="X191" s="1" t="s">
+      <c r="Y191" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="19:24" x14ac:dyDescent="0.3">
-      <c r="V192" s="1" t="s">
+    <row r="192" spans="20:25" x14ac:dyDescent="0.3">
+      <c r="W192" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="X192" s="1" t="s">
+      <c r="Y192" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="193" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V193" s="1" t="s">
+    <row r="193" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W193" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="194" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V194" s="1" t="s">
+    <row r="194" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W194" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="195" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V195" s="1" t="s">
+    <row r="195" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W195" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="196" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V196" s="1" t="s">
+    <row r="196" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W196" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V197" s="1" t="s">
+    <row r="197" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W197" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="198" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V198" s="1" t="s">
+    <row r="198" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W198" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="199" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V199" s="1" t="s">
+    <row r="199" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W199" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="200" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V200" s="1" t="s">
+    <row r="200" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W200" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="X200" s="1" t="s">
+      <c r="Y200" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="201" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V201" s="1" t="s">
+    <row r="201" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W201" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="X201" s="1" t="s">
+      <c r="Y201" s="1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="202" spans="22:24" x14ac:dyDescent="0.3">
-      <c r="V202" s="1" t="s">
+    <row r="202" spans="23:25" x14ac:dyDescent="0.3">
+      <c r="W202" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="X202" s="1" t="s">
+      <c r="Y202" s="1" t="s">
         <v>395</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="P11:P141">
-    <sortCondition ref="P11"/>
+  <sortState ref="Q11:Q141">
+    <sortCondition ref="Q11"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId1"/>
